--- a/docs/Demo - Kagiso Facilities Services (RCOGP)/Kagiso Facilities - BEE Information Gathering FY2025.xlsx
+++ b/docs/Demo - Kagiso Facilities Services (RCOGP)/Kagiso Facilities - BEE Information Gathering FY2025.xlsx
@@ -403,14 +403,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:F10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Measured Entity:</v>
+        <v>Measured Entity: Kagiso Facilities Services (Pty) Ltd</v>
       </c>
       <c r="B1" t="str">
-        <v>Kagiso Facilities Services (Pty) Ltd</v>
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v>Date &amp; Initial:_________________</v>
       </c>
     </row>
     <row r="2">
@@ -431,31 +443,43 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Item</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Amount (ZAR)</v>
+        <v>Turnover /Revenue/ Allocated Budget</v>
+      </c>
+      <c r="B5">
+        <v>24000000</v>
+      </c>
+      <c r="C5">
+        <v>21500000</v>
+      </c>
+      <c r="D5">
+        <v>18800000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Revenue / Turnover</v>
+        <v>NPBT (Nett Profit Before Tax)</v>
       </c>
       <c r="B6">
-        <v>24000000</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Net Profit After Tax (NPAT)</v>
+        <v>NPAT / Loss (Nett Profit After Tax)</v>
       </c>
       <c r="B7">
         <v>1850000</v>
       </c>
+      <c r="C7">
+        <v>1620000</v>
+      </c>
+      <c r="D7">
+        <v>1310000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Leviable Amount (payroll)</v>
+        <v>Annual Payroll</v>
       </c>
       <c r="B8">
         <v>6200000</v>
@@ -463,95 +487,126 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Total Measured Procurement Spend (TMPS)</v>
+        <v>Total Leviable Amount</v>
       </c>
       <c r="B9">
+        <v>6200000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Total Measured Procurement Spend</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10">
         <v>15400000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Shareholder Name</v>
+        <v>Measured Entity: Kagiso Facilities Services (Pty) Ltd</v>
       </c>
       <c r="B1" t="str">
-        <v>Race</v>
+        <v/>
       </c>
       <c r="C1" t="str">
-        <v>Gender</v>
+        <v/>
       </c>
       <c r="D1" t="str">
-        <v>ID Number</v>
+        <v>Ownership Equity</v>
       </c>
       <c r="E1" t="str">
-        <v>Voting Rights %</v>
+        <v/>
       </c>
       <c r="F1" t="str">
-        <v>Economic Interest %</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Number of Shares</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Thabo Molefe</v>
-      </c>
-      <c r="B2" t="str">
-        <v>African</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Male</v>
-      </c>
-      <c r="D2" t="str">
-        <v>8203155012088</v>
-      </c>
-      <c r="E2">
-        <v>60</v>
-      </c>
-      <c r="F2">
-        <v>60</v>
-      </c>
-      <c r="G2">
-        <v>600</v>
+        <v>Date &amp; Initial:_________________</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Shareholder Name</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Race</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ID Number</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Voting Rights %</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Economic Interest %</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Number of Shares</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Thabo Molefe</v>
+      </c>
+      <c r="B4" t="str">
+        <v>African</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Male</v>
+      </c>
+      <c r="D4" t="str">
+        <v>8203155012088</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>Naledi Khumalo</v>
       </c>
-      <c r="B3" t="str">
-        <v>African</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="B5" t="str">
+        <v>African</v>
+      </c>
+      <c r="C5" t="str">
         <v>Female</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D5" t="str">
         <v>8807120145087</v>
       </c>
-      <c r="E3">
+      <c r="E5">
         <v>40</v>
       </c>
-      <c r="F3">
+      <c r="F5">
         <v>40</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>400</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
